--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_LIMITED_ENTRY_MATUREBULL.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_LIMITED_ENTRY_MATUREBULL.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N148"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -668,8 +674,17 @@
           <t>76.9</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>12.8</t>
         </is>
@@ -736,8 +751,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -804,8 +828,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -872,8 +905,17 @@
           <t>40</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -940,8 +982,17 @@
           <t>30.4</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>13.9</t>
         </is>
@@ -1008,8 +1059,17 @@
           <t>31.8</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1076,8 +1136,17 @@
           <t>41.5</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
@@ -1144,8 +1213,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1212,8 +1290,17 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
@@ -1280,8 +1367,17 @@
           <t>37.5</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
@@ -1348,8 +1444,17 @@
           <t>38.9</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>15.1</t>
         </is>
@@ -1416,8 +1521,17 @@
           <t>33.3</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>13.1</t>
         </is>
@@ -1484,8 +1598,17 @@
           <t>55.2</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>15.1</t>
         </is>
@@ -1552,8 +1675,17 @@
           <t>28</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>13.1</t>
         </is>
@@ -1620,8 +1752,17 @@
           <t>25.4</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
@@ -1688,8 +1829,17 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -1756,8 +1906,17 @@
           <t>88.2</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -1824,8 +1983,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1892,8 +2060,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1960,8 +2137,17 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -2028,8 +2214,17 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2096,8 +2291,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -2164,8 +2368,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2232,8 +2445,17 @@
           <t>70.8</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -2300,8 +2522,17 @@
           <t>81.1</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -2368,8 +2599,17 @@
           <t>68.8</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -2436,8 +2676,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -2504,8 +2753,17 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>12.7</t>
         </is>
@@ -2572,8 +2830,17 @@
           <t>47.1</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -2640,8 +2907,17 @@
           <t>42.9</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -2708,8 +2984,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -2776,8 +3061,17 @@
           <t>93.3</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -2844,8 +3138,17 @@
           <t>87.5</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -2912,8 +3215,17 @@
           <t>93.3</t>
         </is>
       </c>
-      <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr">
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -2980,8 +3292,17 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -3048,8 +3369,17 @@
           <t>91.7</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -3116,8 +3446,17 @@
           <t>84.6</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3184,8 +3523,17 @@
           <t>84.2</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -3252,8 +3600,17 @@
           <t>57.9</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
@@ -3320,8 +3677,17 @@
           <t>84.4</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr">
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -3388,8 +3754,17 @@
           <t>78.9</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -3456,8 +3831,17 @@
           <t>70</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -3524,8 +3908,17 @@
           <t>81.8</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -3592,8 +3985,17 @@
           <t>80</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -3660,8 +4062,17 @@
           <t>67.6</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -3728,8 +4139,17 @@
           <t>74</t>
         </is>
       </c>
-      <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -3796,8 +4216,17 @@
           <t>92.9</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -3864,8 +4293,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3932,8 +4370,17 @@
           <t>42.9</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
@@ -4000,8 +4447,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -4068,8 +4524,17 @@
           <t>72.1</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -4136,8 +4601,17 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr">
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -4204,8 +4678,17 @@
           <t>58.3</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -4272,8 +4755,17 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr">
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -4340,8 +4832,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -4408,8 +4909,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -4476,8 +4986,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -4544,8 +5063,17 @@
           <t>76.4</t>
         </is>
       </c>
-      <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -4612,8 +5140,17 @@
           <t>76.5</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -4680,8 +5217,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -4748,8 +5294,17 @@
           <t>65.7</t>
         </is>
       </c>
-      <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -4816,8 +5371,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -4884,8 +5448,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4952,8 +5525,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -5020,8 +5602,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -5088,8 +5679,17 @@
           <t>73.9</t>
         </is>
       </c>
-      <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O69" s="6" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
@@ -5156,8 +5756,17 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -5224,8 +5833,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr">
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O71" s="6" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -5292,8 +5910,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M72" s="4" t="inlineStr"/>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -5360,8 +5987,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr">
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
         <is>
           <t>12.3</t>
         </is>
@@ -5428,8 +6064,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>10.5</t>
         </is>
@@ -5496,8 +6141,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr">
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="inlineStr">
         <is>
           <t>11.5</t>
         </is>
@@ -5564,8 +6218,17 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
@@ -5632,8 +6295,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="6" t="inlineStr">
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -5700,8 +6372,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M78" s="4" t="inlineStr"/>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -5768,8 +6449,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
         <is>
           <t>14.9</t>
         </is>
@@ -5836,8 +6526,17 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O80" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -5904,8 +6603,17 @@
           <t>68.7</t>
         </is>
       </c>
-      <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="6" t="inlineStr">
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -5972,8 +6680,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="O82" s="4" t="inlineStr">
         <is>
           <t>13.7</t>
         </is>
@@ -6040,8 +6757,17 @@
           <t>37.5</t>
         </is>
       </c>
-      <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="6" t="inlineStr">
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="inlineStr">
         <is>
           <t>12.9</t>
         </is>
@@ -6108,8 +6834,17 @@
           <t>22.2</t>
         </is>
       </c>
-      <c r="M84" s="4" t="inlineStr"/>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="M84" s="4" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O84" s="4" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
@@ -6176,8 +6911,17 @@
           <t>42.1</t>
         </is>
       </c>
-      <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="6" t="inlineStr">
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
         <is>
           <t>12.9</t>
         </is>
@@ -6244,8 +6988,17 @@
           <t>61.5</t>
         </is>
       </c>
-      <c r="M86" s="4" t="inlineStr"/>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>10.9</t>
         </is>
@@ -6312,8 +7065,17 @@
           <t>59.3</t>
         </is>
       </c>
-      <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="6" t="inlineStr">
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
@@ -6380,8 +7142,17 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr">
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O88" s="4" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
@@ -6448,8 +7219,17 @@
           <t>72.2</t>
         </is>
       </c>
-      <c r="M89" s="6" t="inlineStr"/>
-      <c r="N89" s="6" t="inlineStr">
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -6516,8 +7296,17 @@
           <t>78.6</t>
         </is>
       </c>
-      <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr">
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -6584,8 +7373,17 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M91" s="6" t="inlineStr"/>
-      <c r="N91" s="6" t="inlineStr">
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
@@ -6652,8 +7450,17 @@
           <t>44.2</t>
         </is>
       </c>
-      <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr">
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O92" s="4" t="inlineStr">
         <is>
           <t>12.7</t>
         </is>
@@ -6720,8 +7527,17 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="6" t="inlineStr">
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O93" s="6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -6788,8 +7604,17 @@
           <t>92.9</t>
         </is>
       </c>
-      <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O94" s="4" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -6856,8 +7681,17 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="M95" s="6" t="inlineStr"/>
-      <c r="N95" s="6" t="inlineStr">
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O95" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -6924,8 +7758,17 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="M96" s="4" t="inlineStr"/>
-      <c r="N96" s="4" t="inlineStr">
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O96" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -6992,8 +7835,17 @@
           <t>81.8</t>
         </is>
       </c>
-      <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="6" t="inlineStr">
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -7060,8 +7912,17 @@
           <t>90</t>
         </is>
       </c>
-      <c r="M98" s="4" t="inlineStr"/>
-      <c r="N98" s="4" t="inlineStr">
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -7128,8 +7989,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="6" t="inlineStr">
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O99" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -7196,8 +8066,17 @@
           <t>89.5</t>
         </is>
       </c>
-      <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O100" s="4" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -7264,8 +8143,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M101" s="6" t="inlineStr"/>
-      <c r="N101" s="6" t="inlineStr">
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr">
         <is>
           <t>6.9</t>
         </is>
@@ -7332,8 +8220,17 @@
           <t>80</t>
         </is>
       </c>
-      <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr">
+      <c r="M102" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -7400,8 +8297,17 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="M103" s="6" t="inlineStr"/>
-      <c r="N103" s="6" t="inlineStr">
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O103" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -7468,8 +8374,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="M104" s="4" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O104" s="4" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -7536,8 +8451,17 @@
           <t>89.3</t>
         </is>
       </c>
-      <c r="M105" s="6" t="inlineStr"/>
-      <c r="N105" s="6" t="inlineStr">
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -7604,8 +8528,17 @@
           <t>43.5</t>
         </is>
       </c>
-      <c r="M106" s="4" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr">
+      <c r="M106" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
         <is>
           <t>12.6</t>
         </is>
@@ -7672,8 +8605,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M107" s="6" t="inlineStr"/>
-      <c r="N107" s="6" t="inlineStr">
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O107" s="6" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
@@ -7740,8 +8682,17 @@
           <t>80</t>
         </is>
       </c>
-      <c r="M108" s="4" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O108" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -7808,8 +8759,17 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="M109" s="6" t="inlineStr"/>
-      <c r="N109" s="6" t="inlineStr">
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O109" s="6" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
@@ -7876,8 +8836,17 @@
           <t>61.5</t>
         </is>
       </c>
-      <c r="M110" s="4" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr">
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -7944,8 +8913,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M111" s="6" t="inlineStr"/>
-      <c r="N111" s="6" t="inlineStr">
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O111" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -8012,8 +8990,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M112" s="4" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="M112" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O112" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -8080,8 +9067,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M113" s="6" t="inlineStr"/>
-      <c r="N113" s="6" t="inlineStr">
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O113" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -8148,8 +9144,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M114" s="4" t="inlineStr"/>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O114" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -8216,8 +9221,17 @@
           <t>53.8</t>
         </is>
       </c>
-      <c r="M115" s="6" t="inlineStr"/>
-      <c r="N115" s="6" t="inlineStr">
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O115" s="6" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -8284,8 +9298,17 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M116" s="4" t="inlineStr"/>
-      <c r="N116" s="4" t="inlineStr">
+      <c r="M116" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O116" s="4" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -8352,8 +9375,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M117" s="6" t="inlineStr"/>
-      <c r="N117" s="6" t="inlineStr">
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O117" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -8420,8 +9452,17 @@
           <t>10</t>
         </is>
       </c>
-      <c r="M118" s="4" t="inlineStr"/>
-      <c r="N118" s="4" t="inlineStr">
+      <c r="M118" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O118" s="4" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -8488,8 +9529,17 @@
           <t>24</t>
         </is>
       </c>
-      <c r="M119" s="6" t="inlineStr"/>
-      <c r="N119" s="6" t="inlineStr">
+      <c r="M119" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O119" s="6" t="inlineStr">
         <is>
           <t>15.3</t>
         </is>
@@ -8556,8 +9606,17 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="M120" s="4" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr">
+      <c r="M120" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -8624,8 +9683,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M121" s="6" t="inlineStr"/>
-      <c r="N121" s="6" t="inlineStr">
+      <c r="M121" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O121" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -8692,8 +9760,17 @@
           <t>72.2</t>
         </is>
       </c>
-      <c r="M122" s="4" t="inlineStr"/>
-      <c r="N122" s="4" t="inlineStr">
+      <c r="M122" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -8760,8 +9837,17 @@
           <t>81.5</t>
         </is>
       </c>
-      <c r="M123" s="6" t="inlineStr"/>
-      <c r="N123" s="6" t="inlineStr">
+      <c r="M123" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O123" s="6" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -8828,8 +9914,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M124" s="4" t="inlineStr"/>
-      <c r="N124" s="4" t="inlineStr">
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
         <is>
           <t>43.7</t>
         </is>
@@ -8896,8 +9991,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M125" s="6" t="inlineStr"/>
-      <c r="N125" s="6" t="inlineStr">
+      <c r="M125" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O125" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -8964,8 +10068,17 @@
           <t>14.3</t>
         </is>
       </c>
-      <c r="M126" s="4" t="inlineStr"/>
-      <c r="N126" s="4" t="inlineStr">
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O126" s="4" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -9032,8 +10145,17 @@
           <t>76</t>
         </is>
       </c>
-      <c r="M127" s="6" t="inlineStr"/>
-      <c r="N127" s="6" t="inlineStr">
+      <c r="M127" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O127" s="6" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
@@ -9100,8 +10222,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M128" s="4" t="inlineStr"/>
-      <c r="N128" s="4" t="inlineStr">
+      <c r="M128" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O128" s="4" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
@@ -9168,8 +10299,17 @@
           <t>59.6</t>
         </is>
       </c>
-      <c r="M129" s="6" t="inlineStr"/>
-      <c r="N129" s="6" t="inlineStr">
+      <c r="M129" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O129" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -9236,8 +10376,17 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="M130" s="4" t="inlineStr"/>
-      <c r="N130" s="4" t="inlineStr">
+      <c r="M130" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
@@ -9304,8 +10453,17 @@
           <t>80</t>
         </is>
       </c>
-      <c r="M131" s="6" t="inlineStr"/>
-      <c r="N131" s="6" t="inlineStr">
+      <c r="M131" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O131" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -9372,8 +10530,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M132" s="4" t="inlineStr"/>
-      <c r="N132" s="4" t="inlineStr">
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O132" s="4" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -9440,8 +10607,17 @@
           <t>72</t>
         </is>
       </c>
-      <c r="M133" s="6" t="inlineStr"/>
-      <c r="N133" s="6" t="inlineStr">
+      <c r="M133" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O133" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -9508,8 +10684,17 @@
           <t>60</t>
         </is>
       </c>
-      <c r="M134" s="4" t="inlineStr"/>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="M134" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O134" s="4" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -9576,8 +10761,17 @@
           <t>86.4</t>
         </is>
       </c>
-      <c r="M135" s="6" t="inlineStr"/>
-      <c r="N135" s="6" t="inlineStr">
+      <c r="M135" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O135" s="6" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -9644,8 +10838,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M136" s="4" t="inlineStr"/>
-      <c r="N136" s="4" t="inlineStr">
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O136" s="4" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -9712,8 +10915,17 @@
           <t>73.7</t>
         </is>
       </c>
-      <c r="M137" s="6" t="inlineStr"/>
-      <c r="N137" s="6" t="inlineStr">
+      <c r="M137" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O137" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -9780,8 +10992,17 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M138" s="4" t="inlineStr"/>
-      <c r="N138" s="4" t="inlineStr">
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -9848,8 +11069,17 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="M139" s="6" t="inlineStr"/>
-      <c r="N139" s="6" t="inlineStr">
+      <c r="M139" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O139" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -9916,8 +11146,17 @@
           <t>88.6</t>
         </is>
       </c>
-      <c r="M140" s="4" t="inlineStr"/>
-      <c r="N140" s="4" t="inlineStr">
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O140" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -9984,8 +11223,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M141" s="6" t="inlineStr"/>
-      <c r="N141" s="6" t="inlineStr">
+      <c r="M141" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O141" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -10052,8 +11300,17 @@
           <t>61.1</t>
         </is>
       </c>
-      <c r="M142" s="4" t="inlineStr"/>
-      <c r="N142" s="4" t="inlineStr">
+      <c r="M142" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -10120,8 +11377,17 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="M143" s="6" t="inlineStr"/>
-      <c r="N143" s="6" t="inlineStr">
+      <c r="M143" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O143" s="6" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -10188,8 +11454,17 @@
           <t>69.4</t>
         </is>
       </c>
-      <c r="M144" s="4" t="inlineStr"/>
-      <c r="N144" s="4" t="inlineStr">
+      <c r="M144" s="4" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
@@ -10256,8 +11531,17 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="M145" s="6" t="inlineStr"/>
-      <c r="N145" s="6" t="inlineStr">
+      <c r="M145" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O145" s="6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -10325,7 +11609,8 @@
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr"/>
-      <c r="N146" s="4" t="inlineStr">
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -10393,7 +11678,8 @@
         </is>
       </c>
       <c r="M147" s="6" t="inlineStr"/>
-      <c r="N147" s="6" t="inlineStr">
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" s="6" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -10460,8 +11746,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M148" s="4" t="inlineStr"/>
-      <c r="N148" s="4" t="inlineStr">
+      <c r="M148" s="4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
